--- a/logs/same_supplier_multi_sts_cases.xlsx
+++ b/logs/same_supplier_multi_sts_cases.xlsx
@@ -2739,12 +2739,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t>Heng Xing 9</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
           <t>Dong Gang You66</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Heng Xing 9</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
+          <t>Bai Da 28</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
           <t>Hai Hang You 7</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Bai Da 28</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">

--- a/logs/same_supplier_multi_sts_cases.xlsx
+++ b/logs/same_supplier_multi_sts_cases.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
